--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E532"/>
+  <dimension ref="A1:E536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12306,11 +12306,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C517" t="inlineStr">
-        <is>
-          <t>504</t>
-        </is>
-      </c>
+      <c r="C517" t="inlineStr"/>
       <c r="D517" t="inlineStr">
         <is>
           <t>04</t>
@@ -12333,11 +12329,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C518" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
+      <c r="C518" t="inlineStr"/>
       <c r="D518" t="inlineStr">
         <is>
           <t>76</t>
@@ -12360,11 +12352,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C519" t="inlineStr">
-        <is>
-          <t>507</t>
-        </is>
-      </c>
+      <c r="C519" t="inlineStr"/>
       <c r="D519" t="inlineStr">
         <is>
           <t>07</t>
@@ -12387,11 +12375,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C520" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
+      <c r="C520" t="inlineStr"/>
       <c r="D520" t="inlineStr">
         <is>
           <t>42</t>
@@ -12724,6 +12708,114 @@
       <c r="E532" t="inlineStr">
         <is>
           <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>13 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>13 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>13 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>13 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E536"/>
+  <dimension ref="A1:E540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12398,11 +12398,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C521" t="inlineStr">
-        <is>
-          <t>981</t>
-        </is>
-      </c>
+      <c r="C521" t="inlineStr"/>
       <c r="D521" t="inlineStr">
         <is>
           <t>81</t>
@@ -12425,11 +12421,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C522" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
+      <c r="C522" t="inlineStr"/>
       <c r="D522" t="inlineStr">
         <is>
           <t>91</t>
@@ -12452,11 +12444,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C523" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
-      </c>
+      <c r="C523" t="inlineStr"/>
       <c r="D523" t="inlineStr">
         <is>
           <t>61</t>
@@ -12479,11 +12467,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C524" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
+      <c r="C524" t="inlineStr"/>
       <c r="D524" t="inlineStr">
         <is>
           <t>51</t>
@@ -12816,6 +12800,114 @@
       <c r="E536" t="inlineStr">
         <is>
           <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>14 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>14 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>439</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>14 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>581</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>14 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>068</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>78</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E540"/>
+  <dimension ref="A1:E544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12490,11 +12490,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C525" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
-      </c>
+      <c r="C525" t="inlineStr"/>
       <c r="D525" t="inlineStr">
         <is>
           <t>52</t>
@@ -12517,11 +12513,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C526" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
+      <c r="C526" t="inlineStr"/>
       <c r="D526" t="inlineStr">
         <is>
           <t>57</t>
@@ -12544,11 +12536,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C527" t="inlineStr">
-        <is>
-          <t>491</t>
-        </is>
-      </c>
+      <c r="C527" t="inlineStr"/>
       <c r="D527" t="inlineStr">
         <is>
           <t>91</t>
@@ -12571,11 +12559,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C528" t="inlineStr">
-        <is>
-          <t>623</t>
-        </is>
-      </c>
+      <c r="C528" t="inlineStr"/>
       <c r="D528" t="inlineStr">
         <is>
           <t>23</t>
@@ -12908,6 +12892,114 @@
       <c r="E540" t="inlineStr">
         <is>
           <t>78</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>15 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>15 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>15 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>996</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>15 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>872</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E544"/>
+  <dimension ref="A1:E548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12582,11 +12582,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C529" t="inlineStr">
-        <is>
-          <t>851</t>
-        </is>
-      </c>
+      <c r="C529" t="inlineStr"/>
       <c r="D529" t="inlineStr">
         <is>
           <t>51</t>
@@ -12609,11 +12605,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C530" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
+      <c r="C530" t="inlineStr"/>
       <c r="D530" t="inlineStr">
         <is>
           <t>57</t>
@@ -12636,11 +12628,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C531" t="inlineStr">
-        <is>
-          <t>963</t>
-        </is>
-      </c>
+      <c r="C531" t="inlineStr"/>
       <c r="D531" t="inlineStr">
         <is>
           <t>63</t>
@@ -12663,11 +12651,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C532" t="inlineStr">
-        <is>
-          <t>569</t>
-        </is>
-      </c>
+      <c r="C532" t="inlineStr"/>
       <c r="D532" t="inlineStr">
         <is>
           <t>69</t>
@@ -13000,6 +12984,114 @@
       <c r="E544" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>16 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>16 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>853</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>16 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>16 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>07</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E548"/>
+  <dimension ref="A1:E552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12674,11 +12674,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C533" t="inlineStr">
-        <is>
-          <t>799</t>
-        </is>
-      </c>
+      <c r="C533" t="inlineStr"/>
       <c r="D533" t="inlineStr">
         <is>
           <t>99</t>
@@ -12701,11 +12697,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C534" t="inlineStr">
-        <is>
-          <t>455</t>
-        </is>
-      </c>
+      <c r="C534" t="inlineStr"/>
       <c r="D534" t="inlineStr">
         <is>
           <t>55</t>
@@ -12728,11 +12720,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C535" t="inlineStr">
-        <is>
-          <t>505</t>
-        </is>
-      </c>
+      <c r="C535" t="inlineStr"/>
       <c r="D535" t="inlineStr">
         <is>
           <t>05</t>
@@ -12755,11 +12743,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C536" t="inlineStr">
-        <is>
-          <t>710</t>
-        </is>
-      </c>
+      <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr">
         <is>
           <t>10</t>
@@ -13092,6 +13076,114 @@
       <c r="E548" t="inlineStr">
         <is>
           <t>07</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>17 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>17 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>853</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>17 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>17 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>082</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>31</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E552"/>
+  <dimension ref="A1:E556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12766,11 +12766,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C537" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
+      <c r="C537" t="inlineStr"/>
       <c r="D537" t="inlineStr">
         <is>
           <t>22</t>
@@ -12793,11 +12789,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C538" t="inlineStr">
-        <is>
-          <t>439</t>
-        </is>
-      </c>
+      <c r="C538" t="inlineStr"/>
       <c r="D538" t="inlineStr">
         <is>
           <t>39</t>
@@ -12820,11 +12812,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C539" t="inlineStr">
-        <is>
-          <t>581</t>
-        </is>
-      </c>
+      <c r="C539" t="inlineStr"/>
       <c r="D539" t="inlineStr">
         <is>
           <t>81</t>
@@ -12847,11 +12835,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C540" t="inlineStr">
-        <is>
-          <t>068</t>
-        </is>
-      </c>
+      <c r="C540" t="inlineStr"/>
       <c r="D540" t="inlineStr">
         <is>
           <t>68</t>
@@ -13184,6 +13168,114 @@
       <c r="E552" t="inlineStr">
         <is>
           <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>18 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>18 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>18 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>18 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>59</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E556"/>
+  <dimension ref="A1:E560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12858,11 +12858,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C541" t="inlineStr">
-        <is>
-          <t>429</t>
-        </is>
-      </c>
+      <c r="C541" t="inlineStr"/>
       <c r="D541" t="inlineStr">
         <is>
           <t>29</t>
@@ -12885,11 +12881,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C542" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
+      <c r="C542" t="inlineStr"/>
       <c r="D542" t="inlineStr">
         <is>
           <t>72</t>
@@ -12912,11 +12904,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C543" t="inlineStr">
-        <is>
-          <t>996</t>
-        </is>
-      </c>
+      <c r="C543" t="inlineStr"/>
       <c r="D543" t="inlineStr">
         <is>
           <t>96</t>
@@ -12939,11 +12927,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C544" t="inlineStr">
-        <is>
-          <t>872</t>
-        </is>
-      </c>
+      <c r="C544" t="inlineStr"/>
       <c r="D544" t="inlineStr">
         <is>
           <t>72</t>
@@ -13276,6 +13260,114 @@
       <c r="E556" t="inlineStr">
         <is>
           <t>59</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>19 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>19 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>19 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>19 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>39</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E560"/>
+  <dimension ref="A1:E564"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13371,6 +13371,114 @@
         </is>
       </c>
     </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>20 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>20 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>20 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>20 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E564"/>
+  <dimension ref="A1:E568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12950,11 +12950,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C545" t="inlineStr">
-        <is>
-          <t>344</t>
-        </is>
-      </c>
+      <c r="C545" t="inlineStr"/>
       <c r="D545" t="inlineStr">
         <is>
           <t>44</t>
@@ -12977,11 +12973,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C546" t="inlineStr">
-        <is>
-          <t>853</t>
-        </is>
-      </c>
+      <c r="C546" t="inlineStr"/>
       <c r="D546" t="inlineStr">
         <is>
           <t>53</t>
@@ -13004,11 +12996,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C547" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
+      <c r="C547" t="inlineStr"/>
       <c r="D547" t="inlineStr">
         <is>
           <t>13</t>
@@ -13031,11 +13019,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C548" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
+      <c r="C548" t="inlineStr"/>
       <c r="D548" t="inlineStr">
         <is>
           <t>58</t>
@@ -13058,11 +13042,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C549" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
+      <c r="C549" t="inlineStr"/>
       <c r="D549" t="inlineStr">
         <is>
           <t>60</t>
@@ -13085,11 +13065,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C550" t="inlineStr">
-        <is>
-          <t>853</t>
-        </is>
-      </c>
+      <c r="C550" t="inlineStr"/>
       <c r="D550" t="inlineStr">
         <is>
           <t>53</t>
@@ -13112,11 +13088,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C551" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
+      <c r="C551" t="inlineStr"/>
       <c r="D551" t="inlineStr">
         <is>
           <t>60</t>
@@ -13139,11 +13111,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C552" t="inlineStr">
-        <is>
-          <t>082</t>
-        </is>
-      </c>
+      <c r="C552" t="inlineStr"/>
       <c r="D552" t="inlineStr">
         <is>
           <t>82</t>
@@ -13476,6 +13444,114 @@
       <c r="E564" t="inlineStr">
         <is>
           <t>61</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>21 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>21 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>917</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>21 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>21 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>90</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E568"/>
+  <dimension ref="A1:E572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13134,11 +13134,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C553" t="inlineStr">
-        <is>
-          <t>367</t>
-        </is>
-      </c>
+      <c r="C553" t="inlineStr"/>
       <c r="D553" t="inlineStr">
         <is>
           <t>67</t>
@@ -13161,11 +13157,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C554" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
+      <c r="C554" t="inlineStr"/>
       <c r="D554" t="inlineStr">
         <is>
           <t>26</t>
@@ -13188,11 +13180,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C555" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
+      <c r="C555" t="inlineStr"/>
       <c r="D555" t="inlineStr">
         <is>
           <t>45</t>
@@ -13215,11 +13203,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C556" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
+      <c r="C556" t="inlineStr"/>
       <c r="D556" t="inlineStr">
         <is>
           <t>37</t>
@@ -13552,6 +13536,114 @@
       <c r="E568" t="inlineStr">
         <is>
           <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>22 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>22 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>078</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>22 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>22 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>48</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E572"/>
+  <dimension ref="A1:E576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13226,11 +13226,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C557" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
+      <c r="C557" t="inlineStr"/>
       <c r="D557" t="inlineStr">
         <is>
           <t>12</t>
@@ -13253,11 +13249,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C558" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
+      <c r="C558" t="inlineStr"/>
       <c r="D558" t="inlineStr">
         <is>
           <t>90</t>
@@ -13280,11 +13272,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C559" t="inlineStr">
-        <is>
-          <t>565</t>
-        </is>
-      </c>
+      <c r="C559" t="inlineStr"/>
       <c r="D559" t="inlineStr">
         <is>
           <t>65</t>
@@ -13307,11 +13295,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C560" t="inlineStr">
-        <is>
-          <t>747</t>
-        </is>
-      </c>
+      <c r="C560" t="inlineStr"/>
       <c r="D560" t="inlineStr">
         <is>
           <t>47</t>
@@ -13644,6 +13628,114 @@
       <c r="E572" t="inlineStr">
         <is>
           <t>48</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>23 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>406</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>23 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>986</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>23 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>083</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>23 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>73</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E576"/>
+  <dimension ref="A1:E580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13739,6 +13739,114 @@
         </is>
       </c>
     </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>24 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>24 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>847</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>24 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>24 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E580"/>
+  <dimension ref="A1:E584"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13318,11 +13318,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C561" t="inlineStr">
-        <is>
-          <t>538</t>
-        </is>
-      </c>
+      <c r="C561" t="inlineStr"/>
       <c r="D561" t="inlineStr">
         <is>
           <t>38</t>
@@ -13345,11 +13341,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C562" t="inlineStr">
-        <is>
-          <t>864</t>
-        </is>
-      </c>
+      <c r="C562" t="inlineStr"/>
       <c r="D562" t="inlineStr">
         <is>
           <t>64</t>
@@ -13372,11 +13364,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C563" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
+      <c r="C563" t="inlineStr"/>
       <c r="D563" t="inlineStr">
         <is>
           <t>49</t>
@@ -13399,11 +13387,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C564" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
+      <c r="C564" t="inlineStr"/>
       <c r="D564" t="inlineStr">
         <is>
           <t>50</t>
@@ -13426,11 +13410,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C565" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
-      </c>
+      <c r="C565" t="inlineStr"/>
       <c r="D565" t="inlineStr">
         <is>
           <t>34</t>
@@ -13453,11 +13433,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C566" t="inlineStr">
-        <is>
-          <t>917</t>
-        </is>
-      </c>
+      <c r="C566" t="inlineStr"/>
       <c r="D566" t="inlineStr">
         <is>
           <t>17</t>
@@ -13480,11 +13456,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C567" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
-      </c>
+      <c r="C567" t="inlineStr"/>
       <c r="D567" t="inlineStr">
         <is>
           <t>40</t>
@@ -13507,11 +13479,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C568" t="inlineStr">
-        <is>
-          <t>766</t>
-        </is>
-      </c>
+      <c r="C568" t="inlineStr"/>
       <c r="D568" t="inlineStr">
         <is>
           <t>66</t>
@@ -13844,6 +13812,114 @@
       <c r="E580" t="inlineStr">
         <is>
           <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>25 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>25 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>712</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>25 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>785</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>25 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>534</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>02</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -13502,11 +13502,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C569" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
+      <c r="C569" t="inlineStr"/>
       <c r="D569" t="inlineStr">
         <is>
           <t>22</t>
@@ -13529,11 +13525,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C570" t="inlineStr">
-        <is>
-          <t>078</t>
-        </is>
-      </c>
+      <c r="C570" t="inlineStr"/>
       <c r="D570" t="inlineStr">
         <is>
           <t>78</t>
@@ -13556,11 +13548,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C571" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
+      <c r="C571" t="inlineStr"/>
       <c r="D571" t="inlineStr">
         <is>
           <t>51</t>
@@ -13583,11 +13571,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C572" t="inlineStr">
-        <is>
-          <t>953</t>
-        </is>
-      </c>
+      <c r="C572" t="inlineStr"/>
       <c r="D572" t="inlineStr">
         <is>
           <t>53</t>
@@ -13610,11 +13594,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C573" t="inlineStr">
-        <is>
-          <t>406</t>
-        </is>
-      </c>
+      <c r="C573" t="inlineStr"/>
       <c r="D573" t="inlineStr">
         <is>
           <t>06</t>
@@ -13637,11 +13617,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C574" t="inlineStr">
-        <is>
-          <t>986</t>
-        </is>
-      </c>
+      <c r="C574" t="inlineStr"/>
       <c r="D574" t="inlineStr">
         <is>
           <t>86</t>
@@ -13664,11 +13640,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C575" t="inlineStr">
-        <is>
-          <t>083</t>
-        </is>
-      </c>
+      <c r="C575" t="inlineStr"/>
       <c r="D575" t="inlineStr">
         <is>
           <t>83</t>
@@ -13691,11 +13663,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C576" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
+      <c r="C576" t="inlineStr"/>
       <c r="D576" t="inlineStr">
         <is>
           <t>18</t>
@@ -13718,11 +13686,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C577" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
+      <c r="C577" t="inlineStr"/>
       <c r="D577" t="inlineStr">
         <is>
           <t>96</t>
@@ -13745,11 +13709,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C578" t="inlineStr">
-        <is>
-          <t>847</t>
-        </is>
-      </c>
+      <c r="C578" t="inlineStr"/>
       <c r="D578" t="inlineStr">
         <is>
           <t>47</t>
@@ -13772,11 +13732,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C579" t="inlineStr">
-        <is>
-          <t>420</t>
-        </is>
-      </c>
+      <c r="C579" t="inlineStr"/>
       <c r="D579" t="inlineStr">
         <is>
           <t>20</t>
@@ -13799,11 +13755,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C580" t="inlineStr">
-        <is>
-          <t>076</t>
-        </is>
-      </c>
+      <c r="C580" t="inlineStr"/>
       <c r="D580" t="inlineStr">
         <is>
           <t>76</t>
@@ -13826,11 +13778,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C581" t="inlineStr">
-        <is>
-          <t>465</t>
-        </is>
-      </c>
+      <c r="C581" t="inlineStr"/>
       <c r="D581" t="inlineStr">
         <is>
           <t>65</t>
@@ -13853,11 +13801,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C582" t="inlineStr">
-        <is>
-          <t>712</t>
-        </is>
-      </c>
+      <c r="C582" t="inlineStr"/>
       <c r="D582" t="inlineStr">
         <is>
           <t>12</t>
@@ -13880,11 +13824,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C583" t="inlineStr">
-        <is>
-          <t>785</t>
-        </is>
-      </c>
+      <c r="C583" t="inlineStr"/>
       <c r="D583" t="inlineStr">
         <is>
           <t>85</t>
@@ -13907,11 +13847,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C584" t="inlineStr">
-        <is>
-          <t>534</t>
-        </is>
-      </c>
+      <c r="C584" t="inlineStr"/>
       <c r="D584" t="inlineStr">
         <is>
           <t>34</t>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E584"/>
+  <dimension ref="A1:E592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13686,7 +13686,11 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C577" t="inlineStr"/>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
       <c r="D577" t="inlineStr">
         <is>
           <t>96</t>
@@ -13709,7 +13713,11 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C578" t="inlineStr"/>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>847</t>
+        </is>
+      </c>
       <c r="D578" t="inlineStr">
         <is>
           <t>47</t>
@@ -13732,7 +13740,11 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C579" t="inlineStr"/>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
       <c r="D579" t="inlineStr">
         <is>
           <t>20</t>
@@ -13755,7 +13767,11 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C580" t="inlineStr"/>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
       <c r="D580" t="inlineStr">
         <is>
           <t>76</t>
@@ -13778,7 +13794,11 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C581" t="inlineStr"/>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>465</t>
+        </is>
+      </c>
       <c r="D581" t="inlineStr">
         <is>
           <t>65</t>
@@ -13801,7 +13821,11 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C582" t="inlineStr"/>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>712</t>
+        </is>
+      </c>
       <c r="D582" t="inlineStr">
         <is>
           <t>12</t>
@@ -13824,7 +13848,11 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C583" t="inlineStr"/>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>785</t>
+        </is>
+      </c>
       <c r="D583" t="inlineStr">
         <is>
           <t>85</t>
@@ -13847,7 +13875,11 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C584" t="inlineStr"/>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>534</t>
+        </is>
+      </c>
       <c r="D584" t="inlineStr">
         <is>
           <t>34</t>
@@ -13856,6 +13888,222 @@
       <c r="E584" t="inlineStr">
         <is>
           <t>02</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>26 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>26 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>26 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>26 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>27 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>27 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>27 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>782</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>27 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>75</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E592"/>
+  <dimension ref="A1:E596"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13686,11 +13686,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C577" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
+      <c r="C577" t="inlineStr"/>
       <c r="D577" t="inlineStr">
         <is>
           <t>96</t>
@@ -13713,11 +13709,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C578" t="inlineStr">
-        <is>
-          <t>847</t>
-        </is>
-      </c>
+      <c r="C578" t="inlineStr"/>
       <c r="D578" t="inlineStr">
         <is>
           <t>47</t>
@@ -13740,11 +13732,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C579" t="inlineStr">
-        <is>
-          <t>420</t>
-        </is>
-      </c>
+      <c r="C579" t="inlineStr"/>
       <c r="D579" t="inlineStr">
         <is>
           <t>20</t>
@@ -13767,11 +13755,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C580" t="inlineStr">
-        <is>
-          <t>076</t>
-        </is>
-      </c>
+      <c r="C580" t="inlineStr"/>
       <c r="D580" t="inlineStr">
         <is>
           <t>76</t>
@@ -14104,6 +14088,114 @@
       <c r="E592" t="inlineStr">
         <is>
           <t>75</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>28 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>28 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>585</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>28 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>758</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>28 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E596"/>
+  <dimension ref="A1:E600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13778,11 +13778,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C581" t="inlineStr">
-        <is>
-          <t>465</t>
-        </is>
-      </c>
+      <c r="C581" t="inlineStr"/>
       <c r="D581" t="inlineStr">
         <is>
           <t>65</t>
@@ -13805,11 +13801,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C582" t="inlineStr">
-        <is>
-          <t>712</t>
-        </is>
-      </c>
+      <c r="C582" t="inlineStr"/>
       <c r="D582" t="inlineStr">
         <is>
           <t>12</t>
@@ -13832,11 +13824,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C583" t="inlineStr">
-        <is>
-          <t>785</t>
-        </is>
-      </c>
+      <c r="C583" t="inlineStr"/>
       <c r="D583" t="inlineStr">
         <is>
           <t>85</t>
@@ -13859,11 +13847,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C584" t="inlineStr">
-        <is>
-          <t>534</t>
-        </is>
-      </c>
+      <c r="C584" t="inlineStr"/>
       <c r="D584" t="inlineStr">
         <is>
           <t>34</t>
@@ -14196,6 +14180,114 @@
       <c r="E596" t="inlineStr">
         <is>
           <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>29 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>29 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>29 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>29 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>67</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E600"/>
+  <dimension ref="A1:E604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13870,11 +13870,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C585" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
+      <c r="C585" t="inlineStr"/>
       <c r="D585" t="inlineStr">
         <is>
           <t>32</t>
@@ -13897,11 +13893,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C586" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
+      <c r="C586" t="inlineStr"/>
       <c r="D586" t="inlineStr">
         <is>
           <t>10</t>
@@ -13924,11 +13916,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C587" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
+      <c r="C587" t="inlineStr"/>
       <c r="D587" t="inlineStr">
         <is>
           <t>84</t>
@@ -13951,11 +13939,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C588" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
-      </c>
+      <c r="C588" t="inlineStr"/>
       <c r="D588" t="inlineStr">
         <is>
           <t>40</t>
@@ -14288,6 +14272,114 @@
       <c r="E600" t="inlineStr">
         <is>
           <t>67</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>30 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>30 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>921</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>30 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>943</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>30 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>52</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E604"/>
+  <dimension ref="A1:E608"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13962,11 +13962,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C589" t="inlineStr">
-        <is>
-          <t>473</t>
-        </is>
-      </c>
+      <c r="C589" t="inlineStr"/>
       <c r="D589" t="inlineStr">
         <is>
           <t>73</t>
@@ -13989,11 +13985,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C590" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
+      <c r="C590" t="inlineStr"/>
       <c r="D590" t="inlineStr">
         <is>
           <t>62</t>
@@ -14016,11 +14008,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C591" t="inlineStr">
-        <is>
-          <t>782</t>
-        </is>
-      </c>
+      <c r="C591" t="inlineStr"/>
       <c r="D591" t="inlineStr">
         <is>
           <t>82</t>
@@ -14043,11 +14031,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C592" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
+      <c r="C592" t="inlineStr"/>
       <c r="D592" t="inlineStr">
         <is>
           <t>36</t>
@@ -14380,6 +14364,114 @@
       <c r="E604" t="inlineStr">
         <is>
           <t>52</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>1 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>1 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>1 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>849</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>1 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>038</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>94</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E608"/>
+  <dimension ref="A1:E612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14475,6 +14475,114 @@
         </is>
       </c>
     </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>018</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>030</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E612"/>
+  <dimension ref="A1:E616"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14054,11 +14054,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C593" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
+      <c r="C593" t="inlineStr"/>
       <c r="D593" t="inlineStr">
         <is>
           <t>15</t>
@@ -14081,11 +14077,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C594" t="inlineStr">
-        <is>
-          <t>585</t>
-        </is>
-      </c>
+      <c r="C594" t="inlineStr"/>
       <c r="D594" t="inlineStr">
         <is>
           <t>85</t>
@@ -14108,11 +14100,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C595" t="inlineStr">
-        <is>
-          <t>758</t>
-        </is>
-      </c>
+      <c r="C595" t="inlineStr"/>
       <c r="D595" t="inlineStr">
         <is>
           <t>58</t>
@@ -14135,11 +14123,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C596" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
+      <c r="C596" t="inlineStr"/>
       <c r="D596" t="inlineStr">
         <is>
           <t>44</t>
@@ -14580,6 +14564,114 @@
       <c r="E612" t="inlineStr">
         <is>
           <t>56</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>3 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>3 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>3 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>948</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>3 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>27</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E616"/>
+  <dimension ref="A1:E620"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14146,11 +14146,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C597" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
+      <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr">
         <is>
           <t>51</t>
@@ -14173,11 +14169,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C598" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
+      <c r="C598" t="inlineStr"/>
       <c r="D598" t="inlineStr">
         <is>
           <t>03</t>
@@ -14200,11 +14192,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C599" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
+      <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr">
         <is>
           <t>08</t>
@@ -14227,11 +14215,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C600" t="inlineStr">
-        <is>
-          <t>419</t>
-        </is>
-      </c>
+      <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr">
         <is>
           <t>19</t>
@@ -14672,6 +14656,114 @@
       <c r="E616" t="inlineStr">
         <is>
           <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>4 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>951</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>4 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>4 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>4 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>96</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E620"/>
+  <dimension ref="A1:E624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14238,11 +14238,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C601" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
+      <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr">
         <is>
           <t>42</t>
@@ -14265,11 +14261,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C602" t="inlineStr">
-        <is>
-          <t>921</t>
-        </is>
-      </c>
+      <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr">
         <is>
           <t>21</t>
@@ -14292,11 +14284,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C603" t="inlineStr">
-        <is>
-          <t>943</t>
-        </is>
-      </c>
+      <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
           <t>43</t>
@@ -14319,11 +14307,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C604" t="inlineStr">
-        <is>
-          <t>417</t>
-        </is>
-      </c>
+      <c r="C604" t="inlineStr"/>
       <c r="D604" t="inlineStr">
         <is>
           <t>17</t>
@@ -14764,6 +14748,114 @@
       <c r="E620" t="inlineStr">
         <is>
           <t>96</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>5 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>5 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>5 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>751</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>5 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>089</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E624"/>
+  <dimension ref="A1:E628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14330,11 +14330,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C605" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
+      <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
         <is>
           <t>08</t>
@@ -14357,11 +14353,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C606" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
+      <c r="C606" t="inlineStr"/>
       <c r="D606" t="inlineStr">
         <is>
           <t>24</t>
@@ -14384,11 +14376,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C607" t="inlineStr">
-        <is>
-          <t>849</t>
-        </is>
-      </c>
+      <c r="C607" t="inlineStr"/>
       <c r="D607" t="inlineStr">
         <is>
           <t>49</t>
@@ -14411,11 +14399,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C608" t="inlineStr">
-        <is>
-          <t>038</t>
-        </is>
-      </c>
+      <c r="C608" t="inlineStr"/>
       <c r="D608" t="inlineStr">
         <is>
           <t>38</t>
@@ -14856,6 +14840,114 @@
       <c r="E624" t="inlineStr">
         <is>
           <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>6 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>6 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>6 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>6 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>53</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1589"/>
+  <dimension ref="A1:F1593"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -51268,6 +51268,134 @@
         </is>
       </c>
     </row>
+    <row r="1590">
+      <c r="A1590" t="inlineStr">
+        <is>
+          <t>7 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C1590" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="D1590" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E1590" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F1590" t="inlineStr">
+        <is>
+          <t>Minh Ngọc+xoso.com.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="inlineStr">
+        <is>
+          <t>7 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1591" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C1591" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="D1591" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E1591" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="F1591" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="inlineStr">
+        <is>
+          <t>7 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1592" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C1592" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="D1592" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E1592" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F1592" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="inlineStr">
+        <is>
+          <t>7 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C1593" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="D1593" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E1593" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="F1593" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1593"/>
+  <dimension ref="A1:F1597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -51396,6 +51396,134 @@
         </is>
       </c>
     </row>
+    <row r="1594">
+      <c r="A1594" t="inlineStr">
+        <is>
+          <t>8 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1594" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C1594" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="D1594" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E1594" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F1594" t="inlineStr">
+        <is>
+          <t>Minh Ngọc+xoso.com.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="inlineStr">
+        <is>
+          <t>8 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1595" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C1595" t="inlineStr">
+        <is>
+          <t>461</t>
+        </is>
+      </c>
+      <c r="D1595" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E1595" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="F1595" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook</t>
+        </is>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="inlineStr">
+        <is>
+          <t>8 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1596" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C1596" t="inlineStr">
+        <is>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="D1596" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E1596" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F1596" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="inlineStr">
+        <is>
+          <t>8 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1597" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C1597" t="inlineStr">
+        <is>
+          <t>829</t>
+        </is>
+      </c>
+      <c r="D1597" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E1597" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F1597" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1597"/>
+  <dimension ref="A1:F1601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -51524,6 +51524,134 @@
         </is>
       </c>
     </row>
+    <row r="1598">
+      <c r="A1598" t="inlineStr">
+        <is>
+          <t>9 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1598" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C1598" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="D1598" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E1598" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="F1598" t="inlineStr">
+        <is>
+          <t>Minh Ngọc+xoso.com.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="inlineStr">
+        <is>
+          <t>9 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1599" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C1599" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="D1599" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E1599" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F1599" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="inlineStr">
+        <is>
+          <t>9 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1600" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C1600" t="inlineStr">
+        <is>
+          <t>007</t>
+        </is>
+      </c>
+      <c r="D1600" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="E1600" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="F1600" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="inlineStr">
+        <is>
+          <t>9 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1601" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C1601" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="D1601" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E1601" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F1601" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1601"/>
+  <dimension ref="A1:F1605"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -51652,6 +51652,134 @@
         </is>
       </c>
     </row>
+    <row r="1602">
+      <c r="A1602" t="inlineStr">
+        <is>
+          <t>10 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1602" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C1602" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D1602" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E1602" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F1602" t="inlineStr">
+        <is>
+          <t>Minh Ngọc+xoso.com.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="inlineStr">
+        <is>
+          <t>10 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1603" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C1603" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="D1603" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E1603" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F1603" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="inlineStr">
+        <is>
+          <t>10 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1604" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C1604" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="D1604" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E1604" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F1604" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="inlineStr">
+        <is>
+          <t>10 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1605" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C1605" t="inlineStr">
+        <is>
+          <t>795</t>
+        </is>
+      </c>
+      <c r="D1605" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E1605" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F1605" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1605"/>
+  <dimension ref="A1:F1609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -51780,6 +51780,134 @@
         </is>
       </c>
     </row>
+    <row r="1606">
+      <c r="A1606" t="inlineStr">
+        <is>
+          <t>11 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1606" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C1606" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="D1606" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E1606" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F1606" t="inlineStr">
+        <is>
+          <t>Minh Ngọc+xoso.com.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="inlineStr">
+        <is>
+          <t>11 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1607" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C1607" t="inlineStr">
+        <is>
+          <t>031</t>
+        </is>
+      </c>
+      <c r="D1607" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E1607" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="F1607" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="inlineStr">
+        <is>
+          <t>11 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1608" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C1608" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="D1608" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E1608" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F1608" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="inlineStr">
+        <is>
+          <t>11 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1609" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C1609" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D1609" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E1609" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="F1609" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1609"/>
+  <dimension ref="A1:F1613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -51908,6 +51908,134 @@
         </is>
       </c>
     </row>
+    <row r="1610">
+      <c r="A1610" t="inlineStr">
+        <is>
+          <t>12 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1610" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C1610" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="D1610" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E1610" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F1610" t="inlineStr">
+        <is>
+          <t>Minh Ngọc+xoso.com.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="inlineStr">
+        <is>
+          <t>12 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C1611" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D1611" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E1611" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="F1611" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="inlineStr">
+        <is>
+          <t>12 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1612" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C1612" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="D1612" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E1612" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F1612" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="inlineStr">
+        <is>
+          <t>12 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1613" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C1613" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="D1613" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E1613" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="F1613" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1613"/>
+  <dimension ref="A1:F1616"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -52036,6 +52036,102 @@
         </is>
       </c>
     </row>
+    <row r="1614">
+      <c r="A1614" t="inlineStr">
+        <is>
+          <t>13 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C1614" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="D1614" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E1614" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="F1614" t="inlineStr">
+        <is>
+          <t>Minh Ngọc+xoso.com.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="inlineStr">
+        <is>
+          <t>13 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C1615" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="D1615" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E1615" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="F1615" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="inlineStr">
+        <is>
+          <t>13 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1616" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C1616" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D1616" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="E1616" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F1616" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1616"/>
+  <dimension ref="A1:F1621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -52132,6 +52132,166 @@
         </is>
       </c>
     </row>
+    <row r="1617">
+      <c r="A1617" t="inlineStr">
+        <is>
+          <t>13 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C1617" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="D1617" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E1617" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="F1617" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook</t>
+        </is>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="inlineStr">
+        <is>
+          <t>14 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1618" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C1618" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D1618" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E1618" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F1618" t="inlineStr">
+        <is>
+          <t>Minh Ngọc+xoso.com.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="inlineStr">
+        <is>
+          <t>14 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1619" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C1619" t="inlineStr">
+        <is>
+          <t>464</t>
+        </is>
+      </c>
+      <c r="D1619" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E1619" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F1619" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="inlineStr">
+        <is>
+          <t>14 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1620" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C1620" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D1620" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="E1620" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F1620" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="inlineStr">
+        <is>
+          <t>14 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1621" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C1621" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="D1621" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E1621" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F1621" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1621"/>
+  <dimension ref="A1:F1625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -52292,6 +52292,134 @@
         </is>
       </c>
     </row>
+    <row r="1622">
+      <c r="A1622" t="inlineStr">
+        <is>
+          <t>15 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1622" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C1622" t="inlineStr">
+        <is>
+          <t>066</t>
+        </is>
+      </c>
+      <c r="D1622" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E1622" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="F1622" t="inlineStr">
+        <is>
+          <t>Minh Ngọc+xoso.com.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="inlineStr">
+        <is>
+          <t>15 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1623" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C1623" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="D1623" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E1623" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F1623" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook</t>
+        </is>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="inlineStr">
+        <is>
+          <t>15 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1624" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C1624" t="inlineStr">
+        <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="D1624" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E1624" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="F1624" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="inlineStr">
+        <is>
+          <t>15 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1625" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C1625" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D1625" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E1625" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="F1625" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1625"/>
+  <dimension ref="A1:F1629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -52420,6 +52420,134 @@
         </is>
       </c>
     </row>
+    <row r="1626">
+      <c r="A1626" t="inlineStr">
+        <is>
+          <t>16 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1626" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C1626" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="D1626" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E1626" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="F1626" t="inlineStr">
+        <is>
+          <t>Minh Ngọc+xoso.com.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="inlineStr">
+        <is>
+          <t>16 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1627" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C1627" t="inlineStr">
+        <is>
+          <t>866</t>
+        </is>
+      </c>
+      <c r="D1627" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E1627" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="F1627" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="inlineStr">
+        <is>
+          <t>16 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1628" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C1628" t="inlineStr">
+        <is>
+          <t>045</t>
+        </is>
+      </c>
+      <c r="D1628" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E1628" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F1628" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="inlineStr">
+        <is>
+          <t>16 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1629" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C1629" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D1629" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E1629" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F1629" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1629"/>
+  <dimension ref="A1:F1633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -52548,6 +52548,134 @@
         </is>
       </c>
     </row>
+    <row r="1630">
+      <c r="A1630" t="inlineStr">
+        <is>
+          <t>17 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1630" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C1630" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D1630" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E1630" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="F1630" t="inlineStr">
+        <is>
+          <t>Minh Ngọc+xoso.com.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="inlineStr">
+        <is>
+          <t>17 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1631" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C1631" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="D1631" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E1631" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F1631" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook</t>
+        </is>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="inlineStr">
+        <is>
+          <t>17 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1632" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C1632" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="D1632" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E1632" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="F1632" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="inlineStr">
+        <is>
+          <t>17 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1633" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C1633" t="inlineStr">
+        <is>
+          <t>457</t>
+        </is>
+      </c>
+      <c r="D1633" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E1633" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="F1633" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1633"/>
+  <dimension ref="A1:F1637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -52676,6 +52676,134 @@
         </is>
       </c>
     </row>
+    <row r="1634">
+      <c r="A1634" t="inlineStr">
+        <is>
+          <t>18 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1634" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C1634" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D1634" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E1634" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F1634" t="inlineStr">
+        <is>
+          <t>Minh Ngọc+xoso.com.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="inlineStr">
+        <is>
+          <t>18 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1635" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C1635" t="inlineStr">
+        <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="D1635" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E1635" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="F1635" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook</t>
+        </is>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="inlineStr">
+        <is>
+          <t>18 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1636" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C1636" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="D1636" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E1636" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1636" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook</t>
+        </is>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="inlineStr">
+        <is>
+          <t>18 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1637" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C1637" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="D1637" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="E1637" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F1637" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1637"/>
+  <dimension ref="A1:F1641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -52804,6 +52804,134 @@
         </is>
       </c>
     </row>
+    <row r="1638">
+      <c r="A1638" t="inlineStr">
+        <is>
+          <t>19 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1638" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C1638" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="D1638" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E1638" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F1638" t="inlineStr">
+        <is>
+          <t>Minh Ngọc+xoso.com.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="inlineStr">
+        <is>
+          <t>19 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1639" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C1639" t="inlineStr">
+        <is>
+          <t>024</t>
+        </is>
+      </c>
+      <c r="D1639" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E1639" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1639" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="inlineStr">
+        <is>
+          <t>19 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1640" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C1640" t="inlineStr">
+        <is>
+          <t>721</t>
+        </is>
+      </c>
+      <c r="D1640" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E1640" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="F1640" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="inlineStr">
+        <is>
+          <t>19 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1641" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C1641" t="inlineStr">
+        <is>
+          <t>791</t>
+        </is>
+      </c>
+      <c r="D1641" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E1641" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F1641" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1641"/>
+  <dimension ref="A1:F1645"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -52932,6 +52932,134 @@
         </is>
       </c>
     </row>
+    <row r="1642">
+      <c r="A1642" t="inlineStr">
+        <is>
+          <t>20 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1642" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C1642" t="inlineStr">
+        <is>
+          <t>809</t>
+        </is>
+      </c>
+      <c r="D1642" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="E1642" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F1642" t="inlineStr">
+        <is>
+          <t>Minh Ngọc+xoso.com.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="inlineStr">
+        <is>
+          <t>20 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1643" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C1643" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="D1643" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E1643" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="F1643" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook</t>
+        </is>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="inlineStr">
+        <is>
+          <t>20 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1644" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C1644" t="inlineStr">
+        <is>
+          <t>752</t>
+        </is>
+      </c>
+      <c r="D1644" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E1644" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F1644" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="inlineStr">
+        <is>
+          <t>20 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1645" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C1645" t="inlineStr">
+        <is>
+          <t>983</t>
+        </is>
+      </c>
+      <c r="D1645" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E1645" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="F1645" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1645"/>
+  <dimension ref="A1:F1649"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -53060,6 +53060,134 @@
         </is>
       </c>
     </row>
+    <row r="1646">
+      <c r="A1646" t="inlineStr">
+        <is>
+          <t>21 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1646" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C1646" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D1646" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E1646" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="F1646" t="inlineStr">
+        <is>
+          <t>Minh Ngọc+xoso.com.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="inlineStr">
+        <is>
+          <t>21 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1647" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C1647" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="D1647" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E1647" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="F1647" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="inlineStr">
+        <is>
+          <t>21 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1648" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C1648" t="inlineStr">
+        <is>
+          <t>034</t>
+        </is>
+      </c>
+      <c r="D1648" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E1648" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F1648" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="inlineStr">
+        <is>
+          <t>21 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1649" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C1649" t="inlineStr">
+        <is>
+          <t>528</t>
+        </is>
+      </c>
+      <c r="D1649" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E1649" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F1649" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1649"/>
+  <dimension ref="A1:F1653"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -53188,6 +53188,134 @@
         </is>
       </c>
     </row>
+    <row r="1650">
+      <c r="A1650" t="inlineStr">
+        <is>
+          <t>22 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1650" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C1650" t="inlineStr">
+        <is>
+          <t>814</t>
+        </is>
+      </c>
+      <c r="D1650" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E1650" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F1650" t="inlineStr">
+        <is>
+          <t>Minh Ngọc+xoso.com.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="inlineStr">
+        <is>
+          <t>22 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1651" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C1651" t="inlineStr">
+        <is>
+          <t>036</t>
+        </is>
+      </c>
+      <c r="D1651" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E1651" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="F1651" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="inlineStr">
+        <is>
+          <t>22 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1652" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C1652" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="D1652" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E1652" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F1652" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="inlineStr">
+        <is>
+          <t>22 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C1653" t="inlineStr">
+        <is>
+          <t>903</t>
+        </is>
+      </c>
+      <c r="D1653" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="E1653" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1653" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1653"/>
+  <dimension ref="A1:F1657"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -53316,6 +53316,134 @@
         </is>
       </c>
     </row>
+    <row r="1654">
+      <c r="A1654" t="inlineStr">
+        <is>
+          <t>23 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1654" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C1654" t="inlineStr">
+        <is>
+          <t>067</t>
+        </is>
+      </c>
+      <c r="D1654" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E1654" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="F1654" t="inlineStr">
+        <is>
+          <t>Minh Ngọc+xoso.com.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="inlineStr">
+        <is>
+          <t>23 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1655" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C1655" t="inlineStr">
+        <is>
+          <t>972</t>
+        </is>
+      </c>
+      <c r="D1655" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E1655" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F1655" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="inlineStr">
+        <is>
+          <t>23 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1656" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C1656" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="D1656" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E1656" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F1656" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="inlineStr">
+        <is>
+          <t>23 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1657" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C1657" t="inlineStr">
+        <is>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="D1657" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E1657" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F1657" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1657"/>
+  <dimension ref="A1:F1661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -53444,6 +53444,134 @@
         </is>
       </c>
     </row>
+    <row r="1658">
+      <c r="A1658" t="inlineStr">
+        <is>
+          <t>24 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1658" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C1658" t="inlineStr">
+        <is>
+          <t>932</t>
+        </is>
+      </c>
+      <c r="D1658" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E1658" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F1658" t="inlineStr">
+        <is>
+          <t>Minh Ngọc+xoso.com.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="inlineStr">
+        <is>
+          <t>24 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1659" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C1659" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="D1659" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E1659" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="F1659" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="inlineStr">
+        <is>
+          <t>24 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1660" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C1660" t="inlineStr">
+        <is>
+          <t>075</t>
+        </is>
+      </c>
+      <c r="D1660" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E1660" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F1660" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="inlineStr">
+        <is>
+          <t>24 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1661" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C1661" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D1661" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E1661" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F1661" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1661"/>
+  <dimension ref="A1:F1665"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -53572,6 +53572,134 @@
         </is>
       </c>
     </row>
+    <row r="1662">
+      <c r="A1662" t="inlineStr">
+        <is>
+          <t>25 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1662" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C1662" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="D1662" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E1662" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F1662" t="inlineStr">
+        <is>
+          <t>Minh Ngọc+xoso.com.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="inlineStr">
+        <is>
+          <t>25 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1663" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C1663" t="inlineStr">
+        <is>
+          <t>086</t>
+        </is>
+      </c>
+      <c r="D1663" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E1663" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F1663" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="inlineStr">
+        <is>
+          <t>25 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1664" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C1664" t="inlineStr">
+        <is>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="D1664" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E1664" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="F1664" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="inlineStr">
+        <is>
+          <t>25 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1665" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C1665" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D1665" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E1665" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F1665" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1665"/>
+  <dimension ref="A1:F1669"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -53700,6 +53700,134 @@
         </is>
       </c>
     </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr">
+        <is>
+          <t>26 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1666" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C1666" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D1666" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E1666" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="F1666" t="inlineStr">
+        <is>
+          <t>Minh Ngọc+xoso.com.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="inlineStr">
+        <is>
+          <t>26 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1667" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C1667" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="D1667" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E1667" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="F1667" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr">
+        <is>
+          <t>26 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1668" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C1668" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="D1668" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E1668" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F1668" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr">
+        <is>
+          <t>26 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C1669" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D1669" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E1669" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="F1669" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1669"/>
+  <dimension ref="A1:F1673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -53828,6 +53828,134 @@
         </is>
       </c>
     </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr">
+        <is>
+          <t>27 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C1670" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="D1670" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E1670" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F1670" t="inlineStr">
+        <is>
+          <t>Minh Ngọc+xoso.com.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr">
+        <is>
+          <t>27 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C1671" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D1671" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E1671" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="F1671" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>27 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C1672" t="inlineStr">
+        <is>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="D1672" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E1672" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F1672" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="inlineStr">
+        <is>
+          <t>27 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C1673" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D1673" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E1673" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F1673" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1673"/>
+  <dimension ref="A1:F1677"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -53956,6 +53956,134 @@
         </is>
       </c>
     </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr">
+        <is>
+          <t>28 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C1674" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D1674" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E1674" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F1674" t="inlineStr">
+        <is>
+          <t>Minh Ngọc+xoso.com.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr">
+        <is>
+          <t>28 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C1675" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="D1675" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E1675" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F1675" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="inlineStr">
+        <is>
+          <t>28 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C1676" t="inlineStr">
+        <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="D1676" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="E1676" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F1676" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="inlineStr">
+        <is>
+          <t>28 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C1677" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="D1677" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="E1677" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F1677" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1677"/>
+  <dimension ref="A1:F1681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -54084,6 +54084,134 @@
         </is>
       </c>
     </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr">
+        <is>
+          <t>29 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1678" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C1678" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="D1678" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="E1678" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F1678" t="inlineStr">
+        <is>
+          <t>Minh Ngọc+xoso.com.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="inlineStr">
+        <is>
+          <t>29 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1679" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C1679" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="D1679" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E1679" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F1679" t="inlineStr">
+        <is>
+          <t>Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="inlineStr">
+        <is>
+          <t>29 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1680" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C1680" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D1680" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E1680" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="F1680" t="inlineStr">
+        <is>
+          <t>Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="inlineStr">
+        <is>
+          <t>29 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1681" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C1681" t="inlineStr">
+        <is>
+          <t>805</t>
+        </is>
+      </c>
+      <c r="D1681" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="E1681" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="F1681" t="inlineStr">
+        <is>
+          <t>Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1681"/>
+  <dimension ref="A1:F1685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -54212,6 +54212,134 @@
         </is>
       </c>
     </row>
+    <row r="1682">
+      <c r="A1682" t="inlineStr">
+        <is>
+          <t>30 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1682" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C1682" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D1682" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E1682" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="F1682" t="inlineStr">
+        <is>
+          <t>Minh Ngọc+xoso.com.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr">
+        <is>
+          <t>30 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1683" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C1683" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="D1683" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E1683" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="F1683" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>30 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C1684" t="inlineStr">
+        <is>
+          <t>024</t>
+        </is>
+      </c>
+      <c r="D1684" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E1684" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F1684" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>30 ต.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C1685" t="inlineStr">
+        <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D1685" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E1685" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F1685" t="inlineStr">
+        <is>
+          <t>บ้านกีฬา+Sanook+สยามรัฐ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
